--- a/docs/i18n/glossary-ko-en.xlsx
+++ b/docs/i18n/glossary-ko-en.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>저장된 설계의 읽기 전용 프로젝션입니다: 배치 순위 · 선택 · 활성 램프 소스 · 기능 그래프를 유형화된 공학 검사와 후보 비교로 보여 줍니다. 형상을 만들거나 타당성을 바꾸거나 순위를 다시 매기지 않습니다. 2중 탈출로는 설계 권고이며 법규 준수 판정이 아닙니다.</t>
+          <t>저장된 설계의 읽기 전용 프로젝션입니다: 배치 순위 · 선택 · 활성 램프 소스 · 용도 그래프(capability graph)를 유형화된 공학 검사와 후보 비교로 보여 줍니다. 형상을 만들거나 실현 가능 여부를 바꾸거나 순위를 다시 매기지 않습니다. 2중 탈출로는 설계 권고이며 법규 준수 판정이 아닙니다.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>활성 설계: 배치 v2 · {id}</t>
+          <t>활성 설계: Layout v2 · {id}</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>활성 설계: 레거시(Hybrid-A*) · 배치 v2 검사는 비활성 배치 선택을 설명합니다</t>
+          <t>활성 설계: 레거시(Hybrid-A*) · Layout v2 검사는 비활성 배치 선택을 설명합니다</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>굴진</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>갱도</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>드리프트</t>
+          <t>하반갱도</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>레벨 개발 가능</t>
+          <t>설계 가능 레벨</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>타당한 후보 없음</t>
+          <t>실현 가능한 후보 없음</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>계획 채광량은 생산 형상(스토프 · 컷 · 채굴 단위) × 밀도로, 계획 수량일 뿐 자원이나 매장량이 아닙니다. 품위 지표는 톤수 가중 계획 대용치로 참고용이며 수익 입력이 아닙니다. 충전과 잔류 광주는 따로 보고하며 생산이 아닙니다.</t>
+          <t>계획 채광량은 생산 형상(채굴장 · 컷 · 채굴 단위) × 밀도로, 계획 수량일 뿐 자원이나 매장량이 아닙니다. 품위 지표는 톤수 가중 계획 대용치로 참고용이며 수익 입력이 아닙니다. 충전과 잔류 광주는 따로 보고하며 생산이 아닙니다.</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>레이즈</t>
+          <t>승갱도</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>비활성 배치 v2 대안입니다. 활성 설계는 레거시 램프를 사용합니다.</t>
+          <t>비활성 Layout v2 대안입니다. 활성 설계는 레거시 램프를 사용합니다.</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>{method} 생산은 이 버전에서 구현되지 않았습니다. 레벨 접근 갱도와 기본 하반 드리프트는 그대로 설계됩니다.</t>
+          <t>{method} 생산은 이 버전에서 구현되지 않았습니다. 레벨 접근 갱도와 기본 하반갱도는 그대로 설계됩니다.</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>레벨 {n}/{total} 개발 가능</t>
+          <t>레벨 {n}/{total} 설계 가능</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>펼침</t>
+          <t>확장 상태</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>기능 할당 중…</t>
+          <t>용도 할당 중…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>기능 구축</t>
+          <t>용도 그래프 구축</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>용도</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>용도</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>기능 재구축</t>
+          <t>용도 그래프 재구축</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>밀폐</t>
+          <t>watertight</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>연결이 어디에 있는지: 갱구 · 램프 분기부 · 레벨 입구 · 분기점 · 채광장 접근 · 수갱 노드를 램프 · 레벨 접근 · 드리프트 · 크로스컷 · 수갱 간선으로 잇는 그래프입니다. 연결성과 지표 탈출 질문에 답하며 일정과 인프라 계획의 바탕이 되는 위상입니다. 부분 수정이 아니라 기준 중심선에서 항상 다시 만듭니다.</t>
+          <t>연결이 어디에 있는지: 갱구 · 램프 분기부 · 레벨 입구 · 분기점 · 채굴장 접근부 · 수갱 노드를 램프 · 레벨 접근 · 하반갱도 · 크로스컷 · 수갱 간선으로 잇는 그래프입니다. 연결성과 지표 탈출 질문에 답하며 일정과 인프라 계획의 바탕이 되는 위상입니다. 부분 수정이 아니라 기준 중심선에서 항상 다시 만듭니다.</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>기준 수명</t>
+          <t>기준 공정 기간</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>기준 수명 {duration} · 작업 {tasks}개</t>
+          <t>기준 공정 기간 {duration} · 작업 {tasks}개</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr"/>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>후보별 비교 개발비(순위 순)</t>
+          <t>후보별 비교 굴진비(순위 순)</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>비교 가능한 타당 후보</t>
+          <t>비교 대상 실현 가능 후보</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>비교 배치 개발비 = 저장된 주 램프 연장 × 램프 단가 + 저장된 레벨 접근 갱도 연장 × 접근 갱도 단가(순위가 매겨진 배치 후보별). 후보가 카탈로그에서 소유한 개발 갱도(주 램프와 레벨 접근 갱도)만 비교하며 드리프트 · 크로스컷 · 수갱 · 생산 · 선광 · 충전 · 고정 운영비 · 자본비 · 수익 · NPV는 제외합니다. 순위 · 1순위 · 선택은 배치 권위가 결정하며 비용으로 바뀌지 않습니다.</t>
+          <t>비교 배치 굴진비 = 저장된 주 램프 연장 × 램프 단가 + 저장된 레벨 접근 갱도 연장 × 접근 갱도 단가(순위가 매겨진 배치 후보별). 후보가 카탈로그에서 소유한 갱도(주 램프와 레벨 접근 갱도)만 비교하며 하반갱도 · 크로스컷 · 수갱 · 생산 · 선광 · 충전 · 고정 운영비 · 자본비 · 수익 · NPV는 제외합니다. 순위 · 1순위 · 선택은 배치 결과가 정하며 비용으로 바뀌지 않습니다.</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr"/>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>개발 갱도</t>
+          <t>굴진</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>개발비</t>
+          <t>굴진비</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>개발비 = 간선 연장 × 간선 유형별 단가(각 개발 작업 기간에 배분). 생산 채광비 = 계획 채광량 × 활성 채광법 단가(채광 구간), 선광비와 총수익은 적재 구간, 컷앤필 충전비는 충전 구간에 배분합니다. 고정 운영비는 광산 수명에 걸쳐 선형, 초기 자본비는 첫 버킷에 둡니다. 기준 계획 NPV = Σ 버킷 순현금흐름 / (1 + 할인율)^(중간일 / 365.25).</t>
+          <t>굴진비 = 간선 연장 × 간선 유형별 단가(각 굴진 작업 기간에 배분). 생산 채광비 = 계획 채광량 × 활성 채광법 단가(채광 구간), 선광비와 총수익은 적재 구간, Cut &amp; Fill 충전비는 충전 구간에 배분합니다. 고정 운영비는 광산 수명에 걸쳐 선형, 초기 자본비는 첫 버킷에 둡니다. 기준 계획 NPV = Σ 버킷 순현금흐름 / (1 + 할인율)^(중간일 / 365.25).</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr"/>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>개발비</t>
+          <t>굴진비</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>개발 굴착(버킷당 m³)</t>
+          <t>갱도 굴착(버킷당 m³)</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr"/>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>계획의 개발 집약도입니다: 계획 채광량 천 톤당 총 굴진 연장과 총 개발 굴착 체적. 계획 채광량이 0이면 정의되지 않습니다(— 표시).</t>
+          <t>계획의 굴진 집약도입니다: 계획 채광량 천 톤당 총 굴진 연장과 총 갱도 굴착 체적. 계획 채광량이 0이면 정의되지 않습니다(— 표시).</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr"/>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>개발 수량은 갱도 네트워크 간선에서 읽습니다: 연장은 간선 유형별 3차원 중심선 길이, 굴착 체적은 간선별 연장 × 단면적의 합입니다. 분기부 중복을 합치지 않은 총(GROSS) 체적입니다. 선언된 네트워크 지표는 간선과 교차 검증하며 덮어쓰지 않습니다.</t>
+          <t>굴진 수량은 갱도 네트워크 간선에서 읽습니다: 연장은 간선 유형별 3차원 중심선 길이, 굴착 체적은 간선별 연장 × 단면적의 합입니다. 분기부 중복을 합치지 않은 총(GROSS) 체적입니다. 선언된 네트워크 지표는 간선과 교차 검증하며 덮어쓰지 않습니다.</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr"/>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>개발 갱도 렌더 메시</t>
+          <t>레벨 갱도 렌더 메시</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>개발 굴착 톤수</t>
+          <t>갱도 굴착 톤수</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr"/>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>개발 굴착 톤수: 미설정 — 굴착 암석을 톤으로 표현하려면 scenario.geology.hostRockDensity를 선언하세요(기본 밀도를 가정하지 않습니다).</t>
+          <t>갱도 굴착 톤수: 미설정 — 굴착 암석을 톤으로 표현하려면 scenario.geology.hostRockDensity를 선언하세요(기본 밀도를 가정하지 않습니다).</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr"/>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>가정 변경 평가(저장 안 됨)</t>
+          <t>What-if 평가(저장 안 됨)</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr"/>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>총 개발 굴착 체적</t>
+          <t>총 갱도 굴착 체적</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>백엔드 레벨 산출물이 보고한, 레벨 개발이 닿지 못한 필수 레벨입니다: 판상 광체의 하반 상단보다 위에 있는 레벨은 위로는 광체가 있어도 옆에 하반 접촉이 없어 드리프트나 크로스컷이 광판에 닿을 수 없고, 그 아래 생산 구간은 미개발로 남습니다. 경사를 고려한 힌트는 모든 레벨에 하반 접촉을 주는 상부 채광 여유입니다.</t>
+          <t>백엔드 레벨 산출물이 보고한, 레벨 갱도가 설계되지 못한 필수 레벨입니다: 판상 광체의 하반 상단보다 위에 있는 레벨은 위로는 광체가 있어도 옆에 하반 접촉이 없어 하반갱도나 크로스컷이 판상 광체에 닿을 수 없고, 그 아래 생산 구간은 미개발로 남습니다. 경사를 고려한 힌트는 모든 레벨에 하반 접촉을 주는 상부 채광 여유입니다.</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr"/>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>점수는 백엔드 배치 v2 계획 비교 지표입니다 · 비교 비용에서 제외: {excluded}</t>
+          <t>점수는 백엔드 Layout v2 계획 비교 지표입니다 · 비교 비용에서 제외: {excluded}</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>개발 작업</t>
+          <t>굴진 작업</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>스토프 생성</t>
+          <t>채굴장 생성</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr"/>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>생산(스토프 · 컷 · 룸)</t>
+          <t>생산(채굴장 · 컷 · 룸)</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>생산 객체 수</t>
+          <t>생산 단위 수</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr"/>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>개발 일정 재생성</t>
+          <t>일정 재생성</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>개발 일정 생성</t>
+          <t>일정 생성</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr"/>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>스토프</t>
+          <t>채굴장</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr"/>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>스토프</t>
+          <t>채굴장</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr"/>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>시나리오 채광법의 계획 생산 체적입니다 — 인접 레벨 사이의 장공 스토프, 1:1 충전이 따르는 컷앤필 리프트의 컷, 또는 잔류 광주를 둔 주방식의 룸(헤딩과 벤치) — 을 백엔드가 레벨 개발에서 생성한 광체 정렬 프리즘으로 보여 줍니다. 체적 · 톤수 · 품위 지표는 결정론적 계획 수량이며 자원 · 매장량 · 타당성 품위 · 지반공학적 광주 설계가 아닙니다.</t>
+          <t>시나리오 채광법의 계획 생산 체적입니다 — 인접 레벨 사이의 장공 채굴장(longhole stope), 1:1 충전이 따르는 Cut &amp; Fill 리프트의 컷, 또는 잔류 광주를 둔 Room &amp; Pillar의 룸(헤딩과 벤치) — 을 백엔드가 레벨 갱도에서 생성한 광체 정렬 프리즘으로 보여 줍니다. 체적 · 톤수 · 품위 지표는 결정론적 계획 수량이며 자원 · 매장량 · 타당성 품위 · 지반공학적 광주 설계가 아닙니다.</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr"/>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>유닛</t>
+          <t>단위</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr"/>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>권위</t>
+          <t>판정 유형</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr"/>
@@ -8540,7 +8540,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>후보 · 패밀리</t>
+          <t>후보 · 유형</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr"/>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>기능 그래프 유효</t>
+          <t>용도 그래프 유효</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr"/>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>개발 갱도 메시</t>
+          <t>레벨 갱도 메시</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr"/>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>개발 갱도 메시(접근 · 드리프트 · 크로스컷)</t>
+          <t>레벨 갱도 메시(접근 · 하반갱도 · 크로스컷)</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr"/>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>드리프트</t>
+          <t>하반갱도</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr"/>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>필수 레벨마다 드리프트와 크로스컷을 램프의 레벨 접근 갱도가 닿는 레벨 입구에 정확히 앵커해 설계합니다. 형상은 백엔드가 소유하며 이 패널은 그것을 보여 줄 뿐입니다.</t>
+          <t>필수 레벨마다 하반갱도(footwall drift)와 크로스컷을 램프의 레벨 접근 갱도가 닿는 레벨 입구에 정확히 앵커해 설계합니다. 형상은 백엔드가 소유하며 이 패널은 그것을 보여 줄 뿐입니다.</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr"/>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>공학 순위(배치 권위)</t>
+          <t>공학 순위(배치 결과 기준)</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>기준 갱구에서 출발하는 램프 패밀리(나선형 · 주향 종단형 · 스위치백)의 유한한 선언 격자를 열거하고, 전달된 모든 중심선을 모든 필수 레벨에 대해 검증한 뒤 타당한 후보에 순위를 매깁니다. 하드 제약은 끝까지 하드입니다: 위반한 후보는 부적합이 되며 점수 페널티로 바뀌지 않습니다. 개발 · 지질 · 기하 점수는 계획 비교 지표일 뿐 비용 추정이나 최적성 주장이 아닙니다.</t>
+          <t>기준 갱구에서 출발하는 램프 유형(나선형 · 주향 평행형 · 스위치백)의 유한한 선언 격자를 열거하고, 전달된 모든 중심선을 모든 필수 레벨에 대해 검증한 뒤 실현 가능한 후보에 순위를 매깁니다. 하드 제약은 끝까지 하드입니다: 위반한 후보는 실현 불가가 되며 점수 페널티로 바뀌지 않습니다. 굴진 · 지질 · 기하 점수는 계획 비교 지표일 뿐 비용 추정이나 최적성 주장이 아닙니다.</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr"/>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>광체 배제 거리</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>타당</t>
+          <t>실현 가능</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr"/>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>개발 갱도 메시 생성</t>
+          <t>레벨 갱도 메시 생성</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr"/>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>레벨 개발 생성</t>
+          <t>레벨 갱도 생성</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr"/>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>부적합</t>
+          <t>실현 불가</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr"/>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>배치 v2</t>
+          <t>Layout v2</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr"/>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>배치 v2 · {id} (활성)</t>
+          <t>Layout v2 · {id} (활성)</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr"/>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>레벨 개발</t>
+          <t>레벨 갱도</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr"/>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>레벨 드리프트(중심선)</t>
+          <t>하반갱도(중심선)</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr"/>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>주향 종단형</t>
+          <t>주향 평행형</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr"/>
@@ -10630,7 +10630,7 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>타당한 후보 없음</t>
+          <t>실현 가능한 후보 없음</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr"/>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>카탈로그에 타당한 후보가 없습니다</t>
+          <t>카탈로그에 실현 가능한 후보가 없습니다</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr"/>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>안 · 패밀리</t>
+          <t>안 · 유형</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr"/>
@@ -10938,7 +10938,7 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>설정 › 접근에서 선언한 선택적 수직 인프라입니다(램프 배치 패밀리가 아님). 이 단계는 선언된 수갱을 레벨 개발에 맞춰 계획합니다: 각 수갱은 지표의 갱구, 기존 레벨 노드에 접속되는 필수 레벨별 스테이션, 바닥 섬프를 가지며 아래의 수갱 메시가 그 계획을 스윕합니다. 선언 자체를 바꾸는 것은 설정 단계의 결정입니다(시나리오가 다시 쓰이고 설계가 초기화됨). 램프는 항상 광산의 주 접근로로 남습니다.</t>
+          <t>설정 › 접근에서 선언한 선택적 수직 인프라입니다(램프 배치 유형이 아님). 이 단계는 선언된 수갱을 레벨 갱도에 맞춰 계획합니다: 각 수갱은 지표의 수갱 갱구, 기존 레벨 노드에 접속되는 필수 레벨별 스테이션, 바닥 섬프를 가지며 아래의 수갱 메시가 그 계획을 스윕합니다. 선언 자체를 바꾸는 것은 설정 단계의 결정입니다(시나리오가 다시 쓰이고 설계가 초기화됨). 램프는 항상 광산의 주 접근로로 남습니다.</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr"/>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>생산 개발 갱도</t>
+          <t>생산 갱도</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr"/>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>개발 갱도 메시 재생성</t>
+          <t>레벨 갱도 메시 재생성</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr"/>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>레벨 개발 재생성</t>
+          <t>레벨 갱도 재생성</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr"/>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>필수 기능 경로</t>
+          <t>필수 용도 경로</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr"/>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>배치 패밀리 탐색 중…</t>
+          <t>램프 배치 유형 탐색 중…</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr"/>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>선택된 후보 타당</t>
+          <t>선택된 후보 실현 가능</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr"/>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>부적합 후보 표시</t>
+          <t>실현 불가 후보 표시</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr"/>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>개발 갱도 메시 스윕 중…</t>
+          <t>레벨 갱도 메시 스윕 중…</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr"/>
@@ -12236,7 +12236,7 @@
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>레벨 접근 갱도 · 드리프트 · 크로스컷 중심선의 굴착 체적으로, 램프 터널과 같은 중력 정렬 단면으로 스윕합니다. 분기부 개구는 유형화된 국부 절단이며 아직 일반 불리언 합집합이 없어 분기부에서 이웃 터널의 안쪽 벽이 보일 수 있습니다.</t>
+          <t>레벨 접근 갱도 · 하반갱도 · 크로스컷 중심선의 굴착 체적으로, 램프 터널과 같은 중력 정렬 단면으로 스윕합니다. 분기부 개구는 유형화된 국부 절단이며 아직 일반 불리언 합집합이 없어 분기부에서 이웃 터널의 안쪽 벽이 보일 수 있습니다.</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr"/>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>램프 굴착 체적입니다: 검증된 램프 중심선을 따라 바닥이 중력에 정렬된 닫힌 튜브를 스윕하므로 단면이 기울지 않습니다. 공칭 체적은 단면적 × 3차원 중심선 길이이며, 닫힌 메시의 부호 체적은 품질 검사로 따로 계산합니다.</t>
+          <t>램프 굴착 체적입니다: 검증된 램프 중심선을 따라 바닥이 중력에 정렬된 닫힌 튜브를 스윕하므로 단면이 기울지 않습니다. 이론 체적은 단면적 × 3차원 중심선 길이이며, 닫힌 메시의 부호 체적은 품질 검사로 따로 계산합니다.</t>
         </is>
       </c>
       <c r="E537" s="2" t="inlineStr"/>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>부적합 사유</t>
+          <t>불가 사유</t>
         </is>
       </c>
       <c r="E543" s="2" t="inlineStr"/>
@@ -12654,7 +12654,7 @@
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
-          <t>{r}개 중 {s}개 스크린 통과</t>
+          <t>{r}개 중 {s}개 선별 통과</t>
         </is>
       </c>
       <c r="E555" s="2" t="inlineStr"/>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>{s}/{r} 스크린 통과</t>
+          <t>{s}/{r} 선별 통과</t>
         </is>
       </c>
       <c r="E556" s="2" t="inlineStr"/>
@@ -13160,7 +13160,7 @@
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
-          <t>핵부 페널티</t>
+          <t>단층핵 페널티</t>
         </is>
       </c>
       <c r="E578" s="2" t="inlineStr"/>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="D579" s="2" t="inlineStr">
         <is>
-          <t>핵부 반폭 m</t>
+          <t>단층핵 반폭 m</t>
         </is>
       </c>
       <c r="E579" s="2" t="inlineStr"/>
@@ -13292,7 +13292,7 @@
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>충전 채광법(컷앤필)</t>
+          <t>충전 채광법(Cut &amp; Fill)</t>
         </is>
       </c>
       <c r="E584" s="2" t="inlineStr"/>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
-          <t>충전 채광법(컷앤필) — 구현됨</t>
+          <t>충전 채광법(Cut &amp; Fill) — 구현됨</t>
         </is>
       </c>
       <c r="E585" s="2" t="inlineStr"/>
@@ -13424,7 +13424,7 @@
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
-          <t>기본 갱구 위치</t>
+          <t>기본 수갱 갱구 위치</t>
         </is>
       </c>
       <c r="E590" s="2" t="inlineStr"/>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="D595" s="2" t="inlineStr">
         <is>
-          <t>명시된 갱구 위치</t>
+          <t>지정한 수갱 갱구 위치</t>
         </is>
       </c>
       <c r="E595" s="2" t="inlineStr"/>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="D606" s="2" t="inlineStr">
         <is>
-          <t>광산 접근 방식입니다: 램프는 항상 존재하며 주 접근로로 남습니다. 선언한 수갱은 추가 수직 인프라(지표의 갱구, 필수 레벨마다 스테이션 하나, 섬프)로, 백엔드가 나중에 설계 › 수갱에서 레벨 개발에 맞춰 계획합니다. 선언은 시나리오 문서의 일부이므로 바꾸면 시나리오가 다시 쓰이고 같은 시드로 월드가 재생성되며 배치 이후가 모두 지워집니다 — 배치 전에 여기서 결정하세요.</t>
+          <t>광산 접근 방식입니다: 램프는 항상 존재하며 주 접근로로 남습니다. 선언한 수갱은 추가 수직 인프라(지표의 수갱 갱구(collar), 필수 레벨마다 스테이션 하나, 섬프)로, 백엔드가 나중에 설계 › 수갱에서 레벨 갱도에 맞춰 계획합니다. 선언은 시나리오 문서의 일부이므로 바꾸면 시나리오가 다시 쓰이고 같은 시드로 월드가 재생성되며 배치 이후가 모두 지워집니다 — 배치 전에 여기서 결정하세요.</t>
         </is>
       </c>
       <c r="E606" s="2" t="inlineStr"/>
@@ -13930,7 +13930,7 @@
       </c>
       <c r="D613" s="2" t="inlineStr">
         <is>
-          <t>장공 개방 채광법</t>
+          <t>장공 개방 채광법(LHOS)</t>
         </is>
       </c>
       <c r="E613" s="2" t="inlineStr"/>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="D614" s="2" t="inlineStr">
         <is>
-          <t>장공 개방 채광법 — 구현됨</t>
+          <t>장공 개방 채광법(LHOS) — 구현됨</t>
         </is>
       </c>
       <c r="E614" s="2" t="inlineStr"/>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="D624" s="2" t="inlineStr">
         <is>
-          <t>공칭 크기</t>
+          <t>기준 크기</t>
         </is>
       </c>
       <c r="E624" s="2" t="inlineStr"/>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="D625" s="2" t="inlineStr">
         <is>
-          <t>공칭 두께</t>
+          <t>기준 두께</t>
         </is>
       </c>
       <c r="E625" s="2" t="inlineStr"/>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="D626" s="2" t="inlineStr">
         <is>
-          <t>공칭 체적</t>
+          <t>이론 체적</t>
         </is>
       </c>
       <c r="E626" s="2" t="inlineStr"/>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="D659" s="2" t="inlineStr">
         <is>
-          <t>주방식 채광법</t>
+          <t>주방식 채광법(Room &amp; Pillar)</t>
         </is>
       </c>
       <c r="E659" s="2" t="inlineStr"/>
@@ -14964,7 +14964,7 @@
       </c>
       <c r="D660" s="2" t="inlineStr">
         <is>
-          <t>주방식 채광법 — 구현됨</t>
+          <t>주방식 채광법(Room &amp; Pillar) — 구현됨</t>
         </is>
       </c>
       <c r="E660" s="2" t="inlineStr"/>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="D674" s="2" t="inlineStr">
         <is>
-          <t>스토프 길이</t>
+          <t>채굴장 길이</t>
         </is>
       </c>
       <c r="E674" s="2" t="inlineStr"/>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="D675" s="2" t="inlineStr">
         <is>
-          <t>스토프 길이 (m)</t>
+          <t>채굴장 길이 (m)</t>
         </is>
       </c>
       <c r="E675" s="2" t="inlineStr"/>
@@ -15382,7 +15382,7 @@
       </c>
       <c r="D679" s="2" t="inlineStr">
         <is>
-          <t>서브레벨</t>
+          <t>레벨 간격</t>
         </is>
       </c>
       <c r="E679" s="2" t="inlineStr"/>
@@ -15404,7 +15404,7 @@
       </c>
       <c r="D680" s="2" t="inlineStr">
         <is>
-          <t>중단 붕락법</t>
+          <t>중단 붕락법(SLC)</t>
         </is>
       </c>
       <c r="E680" s="2" t="inlineStr"/>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="D681" s="2" t="inlineStr">
         <is>
-          <t>중단 붕락법 — 미구현</t>
+          <t>중단 붕락법(SLC) — 미구현</t>
         </is>
       </c>
       <c r="E681" s="2" t="inlineStr"/>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="D684" s="2" t="inlineStr">
         <is>
-          <t>갱구 위치 제안</t>
+          <t>수갱 갱구 위치 제안</t>
         </is>
       </c>
       <c r="E684" s="2" t="inlineStr"/>
@@ -15580,7 +15580,7 @@
       </c>
       <c r="D688" s="2" t="inlineStr">
         <is>
-          <t>채광법은 시나리오 파라미터입니다. 이 버전이 구현한 채광법은 백엔드 레지스트리가 결정합니다: 장공 개방 채광법 · 충전 채광법(컷앤필) · 주방식 채광법은 생산 형상과 일정을 계획하고, 미구현 채광법도 레벨 접근과 기본 하반 드리프트는 받되 다른 채광법의 것으로 대체하지 않습니다. 변경을 적용하면 시나리오가 다시 쓰이고 모든 파생 설계 산출물이 지워지며 같은 시드로 월드가 재생성됩니다.</t>
+          <t>채광법은 시나리오 파라미터입니다. 이 버전이 구현한 채광법은 백엔드 레지스트리가 결정합니다: 장공 개방 채광법(LHOS) · 충전 채광법(Cut &amp; Fill) · 주방식 채광법(Room &amp; Pillar)은 생산 형상과 일정을 계획하고, 미구현 채광법도 레벨 접근과 기본 하반갱도는 받되 다른 채광법의 것으로 대체하지 않습니다. 변경을 적용하면 시나리오가 다시 쓰이고 모든 파생 설계 산출물이 지워지며 같은 시드로 월드가 재생성됩니다.</t>
         </is>
       </c>
       <c r="E688" s="2" t="inlineStr"/>
@@ -15712,7 +15712,7 @@
       </c>
       <c r="D694" s="2" t="inlineStr">
         <is>
-          <t>왜곡 진폭 m</t>
+          <t>굴곡 진폭 m</t>
         </is>
       </c>
       <c r="E694" s="2" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="D695" s="2" t="inlineStr">
         <is>
-          <t>습곡 맥상</t>
+          <t>굴곡 맥상</t>
         </is>
       </c>
       <c r="E695" s="2" t="inlineStr"/>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="D706" s="2" t="inlineStr">
         <is>
-          <t>활성 램프 소스가 배치 v2</t>
+          <t>활성 램프 소스가 Layout v2</t>
         </is>
       </c>
       <c r="E706" s="2" t="inlineStr"/>
@@ -16218,7 +16218,7 @@
       </c>
       <c r="D717" s="2" t="inlineStr">
         <is>
-          <t>네트워크 기능 그래프: 필수 경로와 탈출로 권고</t>
+          <t>네트워크 용도 그래프(capability graph): 필수 경로와 탈출로 권고</t>
         </is>
       </c>
       <c r="E717" s="2" t="inlineStr"/>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="D720" s="2" t="inlineStr">
         <is>
-          <t>통신 장비 배치와 통달 범위 계획</t>
+          <t>통신 장비 배치와 커버리지 계획</t>
         </is>
       </c>
       <c r="E720" s="2" t="inlineStr"/>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="D721" s="2" t="inlineStr">
         <is>
-          <t>통신 라우터 · 통달 범위, 가스 센서 · 감시 범위</t>
+          <t>통신 라우터 · 커버리지, 가스 센서 · 감시 범위</t>
         </is>
       </c>
       <c r="E721" s="2" t="inlineStr"/>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="D739" s="2" t="inlineStr">
         <is>
-          <t>굴착 메시: 램프 터널과 레벨 개발 갱도 스윕</t>
+          <t>굴착 메시: 램프 터널과 레벨 갱도 스윕</t>
         </is>
       </c>
       <c r="E739" s="2" t="inlineStr"/>
@@ -17032,7 +17032,7 @@
       </c>
       <c r="D754" s="2" t="inlineStr">
         <is>
-          <t>비활성 배치 v2</t>
+          <t>비활성 Layout v2</t>
         </is>
       </c>
       <c r="E754" s="2" t="inlineStr"/>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="D762" s="2" t="inlineStr">
         <is>
-          <t>배치 v2</t>
+          <t>Layout v2</t>
         </is>
       </c>
       <c r="E762" s="2" t="inlineStr"/>
@@ -17296,7 +17296,7 @@
       </c>
       <c r="D766" s="2" t="inlineStr">
         <is>
-          <t>레벨 개발: 활성 램프의 접근 갱도 · 드리프트 · 크로스컷</t>
+          <t>레벨 갱도: 활성 램프의 접근 갱도 · 하반갱도 · 크로스컷</t>
         </is>
       </c>
       <c r="E766" s="2" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="D767" s="2" t="inlineStr">
         <is>
-          <t>레벨 개발: 접근 갱도 · 드리프트 · 크로스컷과 굴착 메시</t>
+          <t>레벨 갱도: 접근 갱도 · 하반갱도 · 크로스컷과 굴착 메시</t>
         </is>
       </c>
       <c r="E767" s="2" t="inlineStr"/>
@@ -18044,7 +18044,7 @@
       </c>
       <c r="D800" s="2" t="inlineStr">
         <is>
-          <t>생산 형상(스토프 · 컷 · 룸)</t>
+          <t>생산 형상(채굴장 · 컷 · 룸)</t>
         </is>
       </c>
       <c r="E800" s="2" t="inlineStr"/>
@@ -18110,7 +18110,7 @@
       </c>
       <c r="D803" s="2" t="inlineStr">
         <is>
-          <t>램프 + 개발 갱도</t>
+          <t>램프 + 레벨 갱도</t>
         </is>
       </c>
       <c r="E803" s="2" t="inlineStr"/>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="D821" s="2" t="inlineStr">
         <is>
-          <t>일정: 개발·생산 타임라인(4D)</t>
+          <t>일정: 굴진·생산 타임라인(4D)</t>
         </is>
       </c>
       <c r="E821" s="2" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="D839" s="2" t="inlineStr">
         <is>
-          <t>시간에 따른 개발 진행(4D)</t>
+          <t>시간에 따른 굴진 진행(4D)</t>
         </is>
       </c>
       <c r="E839" s="2" t="inlineStr"/>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="D849" s="2" t="inlineStr">
         <is>
-          <t>{feasible} / {total} 타당</t>
+          <t>{feasible} / {total} 실현 가능</t>
         </is>
       </c>
       <c r="E849" s="2" t="inlineStr"/>
@@ -19144,7 +19144,7 @@
       </c>
       <c r="D850" s="2" t="inlineStr">
         <is>
-          <t>{total}개 열거 중 {feasible}개 타당</t>
+          <t>{total}개 열거 중 {feasible}개 실현 가능</t>
         </is>
       </c>
       <c r="E850" s="2" t="inlineStr"/>
@@ -19188,7 +19188,7 @@
       </c>
       <c r="D852" s="2" t="inlineStr">
         <is>
-          <t>기능 {n}개</t>
+          <t>용도 {n}개</t>
         </is>
       </c>
       <c r="E852" s="2" t="inlineStr"/>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="D853" s="2" t="inlineStr">
         <is>
-          <t>기능 {n}개</t>
+          <t>용도 {n}개</t>
         </is>
       </c>
       <c r="E853" s="2" t="inlineStr"/>
@@ -19320,7 +19320,7 @@
       </c>
       <c r="D858" s="2" t="inlineStr">
         <is>
-          <t>레벨 {n}개 개발 가능</t>
+          <t>설계 가능 레벨 {n}개</t>
         </is>
       </c>
       <c r="E858" s="2" t="inlineStr"/>
@@ -19716,7 +19716,7 @@
       </c>
       <c r="D876" s="2" t="inlineStr">
         <is>
-          <t>통신 통달 범위</t>
+          <t>통신 커버리지</t>
         </is>
       </c>
       <c r="E876" s="2" t="inlineStr"/>
@@ -19760,7 +19760,7 @@
       </c>
       <c r="D878" s="2" t="inlineStr">
         <is>
-          <t>통달 / 백홀 거리</t>
+          <t>커버리지 / 백홀 거리</t>
         </is>
       </c>
       <c r="E878" s="2" t="inlineStr"/>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="D879" s="2" t="inlineStr">
         <is>
-          <t>통달 거리</t>
+          <t>커버리지 거리</t>
         </is>
       </c>
       <c r="E879" s="2" t="inlineStr"/>
@@ -20090,7 +20090,7 @@
       </c>
       <c r="D893" s="2" t="inlineStr">
         <is>
-          <t>요구 통달 범위</t>
+          <t>요구 커버리지</t>
         </is>
       </c>
       <c r="E893" s="2" t="inlineStr"/>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="D898" s="2" t="inlineStr">
         <is>
-          <t>갱내 메시 라우터 배치와 백홀 계획입니다. 통달 범위와 백홀은 암반을 직선으로 관통하지 않고 실제 갱도 네트워크를 따라 측정하며, 선택된 모든 라우터는 갱구까지 연결됩니다. 명시적 계획 대용 모델일 뿐 보정된 전파 예측도 전역 최적 설계도 아니며 라우터 설치 시기는 모델링하지 않습니다.</t>
+          <t>갱내 메시 라우터 배치와 백홀 계획입니다. 커버리지와 백홀은 암반을 직선으로 관통하지 않고 실제 갱도 네트워크를 따라 측정하며, 선택된 모든 라우터는 갱구까지 연결됩니다. 명시적 계획 대용 모델일 뿐 보정된 전파 예측도 전역 최적 설계도 아니며 라우터 설치 시기는 모델링하지 않습니다.</t>
         </is>
       </c>
       <c r="E898" s="2" t="inlineStr"/>
@@ -20218,7 +20218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -20314,12 +20314,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>습곡 맥상 광체</t>
+          <t>굴곡 맥상 광체</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>저주파 변형(warp)을 가진 맥(vein)형 광체. 합성 형태이며 실측 광체가 아님.</t>
+          <t>'습곡(褶曲)'은 지층이 지각변동으로 접힌 구조(fold)를 뜻함. 이 광체는 맥 중심면이 저주파로 휘고(warp) 두께가 변하는 합성 형태라 습곡과 무관. '굴곡'(휘어짐)이 원어에 가깝고, 형태 전반을 강조하려면 README 명칭(irregular warped vein)을 따른 '불규칙 맥상 광체'도 가능. UI #54·#55 수정안 기입.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -20365,7 +20365,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>傾斜. 경사 방향 = 주향 + 90°(우수법칙).</t>
+          <t>傾斜. 경사 방향 = 주향 + 90°(오른손 법칙).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -20475,12 +20475,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>단층 핵부 / 손상대</t>
+          <t>단층핵 / 단층 손상대</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>핵부 반폭·영향 반폭(규칙 36).</t>
+          <t>국내 구조지질 문헌 표기(예: '단층 손상대 내 분쇄암의 진화', 경상국립대). '핵부'도 이해되지만 문헌과 맞추려면 '단층핵'. UI #7·#59 수정안 기입.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -20603,22 +20603,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>접근·갱도</t>
+          <t>지질·광상</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Ramp / decline</t>
+          <t>Nominal (size / thickness)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>램프(사갱)</t>
+          <t>기준 크기 / 기준 두께</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>斜坑. 현장에서는 '램프' 또는 '경사 갱도'가 통용. 표기: 램프.</t>
+          <t>굴곡 맥상 광체의 설정 치수(길이 L, 경사 방향 높이 H, 두께 T). 형태 모델이 위치별로 이 값을 늘이고 줄임.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -20631,17 +20631,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Ramp / decline</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>갱구</t>
+          <t>램프(사갱)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>坑口. 램프의 지표 입구.</t>
+          <t>斜坑. 현장에서는 '램프' 또는 '경사 갱도'가 통용. 표기: 램프. 검토(2026-10): SNU OCW: Ramp = 레벨을 잇는 하향 2·3차 사갱(운반갱도로 사용), Slope = 지표와 채굴장을 잇는 1차 사갱도. HRM은 곡선이 있는 고무바퀴 장비용 갱도를 ramp, 직선(컨베이어) 갱도를 decline으로 구분. MineGen 주 접근로는 나선·스위치백 곡선이므로 '램프'가 맞고, 영어가 decline인 레거시 Hybrid-A* 항목만 '사갱' 유지.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -20654,17 +20654,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Shaft</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>수갱</t>
+          <t>갱구</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>竪坑. 수직 갱도(권양용).</t>
+          <t>坑口. 램프의 지표 입구.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -20677,17 +20677,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Shaft collar</t>
+          <t>Shaft</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>수갱 갱구(콜라)</t>
+          <t>수갱</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>수갱의 지표부. 현장 용어 '콜라'.</t>
+          <t>竪坑. 수직 갱도(권양용).</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -20700,17 +20700,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Shaft station</t>
+          <t>Shaft collar</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>수갱 스테이션</t>
+          <t>수갱 갱구(칼라)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>각 레벨과 수갱이 만나는 접속부(중단 접속).</t>
+          <t>외래어 표기 collar = '칼라'('콜라'는 음료로 읽힘). UI에서 단독 '갱구'는 램프 Portal과 겹치므로 수갱 맥락은 '수갱 갱구'로 명시(UI #83·#85·#137·#143·#203).</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -20723,17 +20723,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Sump</t>
+          <t>Shaft station</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>섬프</t>
+          <t>수갱 스테이션</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>수갱 최하부 집수부.</t>
+          <t>각 레벨과 수갱이 만나는 접속부.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -20746,17 +20746,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Sump</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>레벨</t>
+          <t>섬프</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>갱도 중단(中段). 현장 통용은 '레벨'(예: L01).</t>
+          <t>수갱 최하부 집수부. 검토(2026-10): 터널·토목 표준어는 '집수정(集水井)'. UI는 '섬프' 유지 가능, 처음 설명하는 문장에서 '집수정(섬프)' 병기는 선택.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -20769,17 +20769,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Sublevel interval</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>레벨 간격</t>
+          <t>레벨</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>서브레벨 간 수직 간격(m).</t>
+          <t>편(片)·작업 레벨. 광산안전기술기준은 레벨을 '편'(가행 편수, 각 편이 수갱 등으로 연결), SNU OCW는 '수갱에 연결된 수평갱도, 작업층'으로 정의. 현장 통용은 '레벨'(예: L01). '중단(中段)'은 sublevel(중단채굴법·중단붕락법)이므로 레벨의 뜻으로 쓰지 않음.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -20792,17 +20792,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Level access</t>
+          <t>Sublevel interval</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>레벨 접근 갱도</t>
+          <t>레벨 간격</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>램프 분기부에서 레벨 입구까지의 분기 갱도.</t>
+          <t>레벨(중단) 간 수직 간격(m). 검토(2026-10): MineGen에서 이 값은 생성되는 레벨(L01…) 사이 수직 간격이라 UI는 '레벨 간격'이 혼동이 적음. 일반 용어로 sublevel = 중단(SNU OCW: 주요 레벨 사이의 2차·중간 레벨). 근거 열 '레벨(중단) 간 수직 간격' → '레벨(중단) 간 수직 간격'. 레거시 패널의 'Sublevel'(#254)도 '레벨 간격'으로 통일. MineGen에서 이 값은 생성되는 레벨(L01…) 사이 수직 간격이라 UI는 '레벨 간격'; 일반 용어 sublevel = 중단. 레거시 패널의 'Sublevel'도 '레벨 간격'으로 통일.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -20815,17 +20815,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Ramp junction (turnout)</t>
+          <t>Level access</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>램프 분기부</t>
+          <t>레벨 접근 갱도</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>램프에서 레벨 접근 갱도가 갈라지는 지점.</t>
+          <t>램프 분기부에서 레벨 입구까지의 분기 갱도.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -20838,17 +20838,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Level entry</t>
+          <t>Ramp junction (turnout)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>레벨 입구</t>
+          <t>램프 분기부</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>레벨 개발 갱도(드리프트)가 시작되는 점.</t>
+          <t>램프에서 레벨 접근 갱도가 갈라지는 지점.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -20861,17 +20861,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Drift (footwall drive)</t>
+          <t>Level entry</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>드리프트(하반 주향 갱도)</t>
+          <t>레벨 입구</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>주향 방향 수평 갱도. '하반 갱도'와 혼용.</t>
+          <t>하반갱도가 시작되는 점.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -20884,17 +20884,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Crosscut</t>
+          <t>Drift (footwall drive)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>크로스컷(횡갱)</t>
+          <t>하반갱도</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>橫坑. 드리프트에서 광체로 직교 진입하는 갱도.</t>
+          <t>MineGen의 DRIFT는 레벨 입구에서 시작해 광체 밖 하반 이격(기본 20 m) 위치에서 하반을 따라가는 레벨 백본(판상은 주향과 평행, WARPED는 곡선)이므로 '하반갱도'(footwall drift). 근거: HRM 'Footwall drifts … should be offset from the ore by at least 15 m', 상동광산 연혁 '상동갱 하반갱도 굴착(1959)', SME 'Drift: in or near an ore body and parallel to the course of the vein'. '(하반 주향 갱도)'의 '주향'은 WARPED 곡선 레벨과 맞지 않음. SNU OCW는 drift를 '연층갱도'로 옮기나 탄층 굴진 어감이 강하고 광체 '안'을 연상시켜 부적합. 방향과 무관한 일반 drift는 신규 행 '수평갱도'. UI 13건 수정안 기입.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -20907,17 +20907,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Raise</t>
+          <t>Crosscut</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>레이즈(승갱)</t>
+          <t>크로스컷</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>昇坑. 상향 수직·급경사 갱도(미구현).</t>
+          <t>현장 표기 'Cross'(상동광산 연혁 'Cross 굴착·개설'), SNU OCW 정의 '연층갱도·채굴갱도 등을 연결하는 3차 수평갱도'. '횡갱'은 이번 검토에서 문헌 용례를 확인하지 못했고 일반 '수평 갱도'로도 읽혀 병기 생략 권장. 근거 열 '하반갱도에서 광체 방향으로 낸 수평갱도(판상은 주향 직교, WARPED는 국부 법선)' → '하반갱도에서 광체 방향으로 낸 수평갱도(판상은 주향 직교, WARPED는 국부 법선)'.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -20930,17 +20930,17 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Raise</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>개발 갱도(굴진)</t>
+          <t>승갱도(레이즈)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>생산 전 선행 갱도 굴진 전체. 수량은 '굴진 연장(m)'.</t>
+          <t>광산안전기술기준 제51조 '승갱도', SNU OCW 'Raise: 레벨을 연결하는 상향 2·3차 갱도'(하향은 winze). UI #460 수정안 기입.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -20953,17 +20953,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Excavation</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>굴착</t>
+          <t>굴진(갱도)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>터널 굴착 체적·메시.</t>
+          <t>안내 시트 예시처럼 현장에서는 '레벨 개발'보다 '레벨 갱도'. 수량·비용·작업은 '굴진'(굴진 연장·굴진비·굴진 작업), 대상은 '갱도'(레벨 갱도·생산 갱도)로 구분. '개발'이 R&amp;D 개발로 읽히는 것도 피함. 단 '광산 개발 흐름·광산 개발 일정'처럼 광산 전체를 가리킬 때는 유지. UI 약 35건 수정안 기입.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -20976,17 +20976,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Tunnel mesh</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>터널 메시</t>
+          <t>굴착</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>램프 굴착 단면 스윕 메시.</t>
+          <t>터널 굴착 체적·메시.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -20999,17 +20999,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Development mesh</t>
+          <t>Tunnel mesh</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>개발 갱도 메시</t>
+          <t>터널 메시</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>레벨 접근·드리프트·크로스컷 스윕 메시.</t>
+          <t>램프 굴착 단면 스윕 메시.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -21022,17 +21022,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Gradient</t>
+          <t>Development mesh</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>구배</t>
+          <t>레벨 갱도 메시</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>勾配. 수직/수평 비(예: 12 %). 현장 표기 '구배'.</t>
+          <t>대상이 레벨 접근 갱도·하반갱도·크로스컷이므로 '레벨 갱도 메시'.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -21045,17 +21045,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Minimum turning radius</t>
+          <t>Gradient</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>최소 회전 반경</t>
+          <t>구배</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>램프 평면 곡률 제한.</t>
+          <t>勾配. 수직/수평 비(예: 12 %). 현장 표기 '구배'.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -21068,17 +21068,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Minimum surface cover</t>
+          <t>Minimum turning radius</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>최소 토피</t>
+          <t>최소 회전 반경</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>土被. 지표에서 갱도까지의 최소 암반 두께.</t>
+          <t>램프 평면 곡률 제한.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -21091,17 +21091,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Clearance (orebody)</t>
+          <t>Minimum surface cover</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>광체 이격 거리</t>
+          <t>최소 토피</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>갱도 중심선과 광체 표면 사이 요구 거리.</t>
+          <t>土被. 지표에서 갱도까지의 최소 암반 두께.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -21114,17 +21114,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Footwall access offset</t>
+          <t>Clearance (orebody)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>하반 접근 이격</t>
+          <t>광체 이격 거리</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>레벨 개발 갱도가 하반에서 떨어지는 거리(기본 20 m).</t>
+          <t>갱도 중심선과 광체 표면 사이 요구 거리.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -21137,17 +21137,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Rock pillar (between drives)</t>
+          <t>Footwall access offset</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>갱도 간 암반 필러</t>
+          <t>하반 접근 이격</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>인접 갱도 사이에 남기는 암반 두께.</t>
+          <t>레벨 개발 갱도가 하반에서 떨어지는 거리(기본 20 m).</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -21160,17 +21160,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Restricted zone</t>
+          <t>Rock pillar (between drives)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>제한 구역</t>
+          <t>갱도 간 암주</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>설계 금지 구역.</t>
+          <t>국내 지하공간 문헌의 '암주(岩柱)'(한국터널지하공간학회 논문집, 주방식 지하구조물 연구 2015·2016). 광주(鑛柱)·필러와 구분됨.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -21178,22 +21178,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>배치(레이아웃)</t>
+          <t>접근·갱도</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Layout</t>
+          <t>Restricted zone</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>갱도 배치</t>
+          <t>제한 구역</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>램프 패밀리·레벨 접근의 전체 배치안. UI 카드명 '광산 배치'.</t>
+          <t>설계 금지 구역.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -21201,22 +21201,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>배치(레이아웃)</t>
+          <t>접근·갱도</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Candidate / Option</t>
+          <t>Drift (general lateral heading)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>후보 / 안(案)</t>
+          <t>수평갱도</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>UI에서는 'Option n' → 'n안'.</t>
+          <t>방향과 무관한 일반 수평 굴진 갱도(HRM의 'lateral development / lateral heading'). SNU OCW: Level = '수갱에 연결된 수평갱도', Haulageway = '주로 재료운반에 사용되는 수평갱도'. MineGen의 DRIFT 간선은 모두 하반갱도라 현재 UI에는 쓰이지 않음.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -21224,22 +21224,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>배치(레이아웃)</t>
+          <t>접근·갱도</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Spiral</t>
+          <t>Ore drive / vein drift</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>나선형</t>
+          <t>연맥갱도(금속광) / 연층갱도(석탄)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>나선 램프(SPIRAL).</t>
+          <t>광체(맥·탄층) 안에서 주향을 따라 내는 갱도. SNU OCW는 drift를 '연층(沿層)갱도'로 번역(탄층 기준 어감). 금속광은 '연맥(沿脈)'. MineGen에는 현재 없는 요소이며 향후 생산 갱도 구분용. (참고: '연맥갱도'는 이번 검토에서 문헌 출처를 확인하지 못함 — 확인 후 채택)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -21247,22 +21247,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>배치(레이아웃)</t>
+          <t>접근·갱도</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Switchback</t>
+          <t>Haulageway</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>스위치백</t>
+          <t>운반갱도</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>절환식 지그재그 램프.</t>
+          <t>광석·자재 운반용 주 수평갱도. SNU OCW('주로 재료운반에 사용되는 수평갱도'), 광산안전기술기준 제80조('주요운반갱도'), 상동광산 연혁('백운갱 운반갱도 설치') 공통.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -21270,22 +21270,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>배치(레이아웃)</t>
+          <t>접근·갱도</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Longitudinal</t>
+          <t>Sublevel</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>주향 종단형</t>
+          <t>중단(서브레벨)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>주향 방향으로 길게 내려가는 램프.</t>
+          <t>주요 레벨 사이의 2차·중간 레벨(SNU OCW). 중단채굴법(sublevel stoping)·중단붕락법(sublevel caving)과 같은 계열. MineGen UI의 sublevelInterval 표시는 '레벨 간격' 유지.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -21293,22 +21293,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>배치(레이아웃)</t>
+          <t>접근·갱도</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Hairpin</t>
+          <t>Nominal (excavation) volume</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>헤어핀</t>
+          <t>이론 체적</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>180° 전환 구간.</t>
+          <t>단면적 × 3차원 중심선 길이(경사 보정 없음). 닫힌 메시의 부호 체적은 별도 품질 검사.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -21316,22 +21316,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>배치(레이아웃)</t>
+          <t>접근·갱도</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Ranking winner</t>
+          <t>Watertight (mesh)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>1순위 안</t>
+          <t>watertight</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>공학 점수 기준 최상위 후보.</t>
+          <t>구멍 없이 닫힌 메시(매니폴드). 터널 메시 품질 표시.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -21344,17 +21344,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Selected / Active</t>
+          <t>Layout</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>선택 / 활성</t>
+          <t>갱도 배치</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>선택 = 선정만, 활성 = 현재 설계로 채택.</t>
+          <t>램프 패밀리·레벨 접근의 전체 배치안. UI 카드명 '광산 배치'.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -21367,17 +21367,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Feasible / Infeasible</t>
+          <t>Candidate / Option</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>타당 / 부적합</t>
+          <t>후보 / 안(案)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>하드 제약 통과 여부.</t>
+          <t>UI에서는 'Option n' → 'n안'.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -21390,17 +21390,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Engineering rank</t>
+          <t>Spiral</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>공학 순위</t>
+          <t>나선형</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>비용과 분리된 설계 점수 순위(규칙 206).</t>
+          <t>나선 램프(SPIRAL).</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -21408,22 +21408,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>채광</t>
+          <t>배치(레이아웃)</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Mining method</t>
+          <t>Switchback</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>채광법</t>
+          <t>스위치백</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>採鑛法.</t>
+          <t>절환식 지그재그 램프.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -21431,22 +21431,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>채광</t>
+          <t>배치(레이아웃)</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Longhole open stoping</t>
+          <t>Longitudinal</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>장공 개방 채광법</t>
+          <t>주향 평행형</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>롱홀 스토핑. 현장 약칭 '롱홀'.</t>
+          <t>'종단'은 국내 토목에서 종단면(vertical profile, #858 '사갱 종단면')을 뜻해 혼동. 이 유형은 하반갱도와 나란히 주향을 따라 내려가는 램프. 영어 'Longitudinal'을 그대로 쓰는 것도 가능</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -21454,22 +21454,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>채광</t>
+          <t>배치(레이아웃)</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Cut and fill</t>
+          <t>Hairpin</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>충전 채광법(컷앤필)</t>
+          <t>헤어핀</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>절삭 후 충전을 반복하는 채광법.</t>
+          <t>180° 전환 구간.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -21477,22 +21477,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>채광</t>
+          <t>배치(레이아웃)</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Room and pillar</t>
+          <t>Ranking winner</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>주방식 채광법</t>
+          <t>1순위 안</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>柱房式. 룸앤필러.</t>
+          <t>공학 점수 기준 최상위 후보.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -21500,22 +21500,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>채광</t>
+          <t>배치(레이아웃)</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Sublevel caving</t>
+          <t>Selected / Active</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>중단 붕락법</t>
+          <t>선택 / 활성</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>미구현(예약).</t>
+          <t>선택 = 선정만, 활성 = 현재 설계로 채택.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -21523,22 +21523,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>채광</t>
+          <t>배치(레이아웃)</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Shrinkage stoping</t>
+          <t>Feasible / Infeasible</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>슈링키지 채광법</t>
+          <t>실현 가능 / 실현 불가</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>미구현(예약).</t>
+          <t>'타당'은 '타당성 조사(feasibility study)'를 연상시키는데, 앱은 경제성이 타당성 조사가 아님을 명시함. 하드 제약 통과 여부이므로 최적화 용어 '실현 가능'이 정확하고, '타당/부적합'은 짝도 맞지 않음. UI 15건 수정안 기입('타당성 품위·타당성 조사'는 원뜻이라 유지).</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -21546,22 +21546,22 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>채광</t>
+          <t>배치(레이아웃)</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Stope</t>
+          <t>Engineering rank</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>스토프(채광장)</t>
+          <t>공학 순위</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>採鑛場. 생산 채굴 단위 공간. 채굴 후 공동은 '채굴적'.</t>
+          <t>비용과 분리된 설계 점수 순위(규칙 206).</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -21569,22 +21569,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>채광</t>
+          <t>배치(레이아웃)</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Stope access</t>
+          <t>Orebody exclusion buffer</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>채광장 접근</t>
+          <t>광체 배제 거리</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>크로스컷 종점(채광장 진입점).</t>
+          <t>설계 갱도가 광체에 들어가지 않도록 두는 거리(기본 5 m). 레거시 패널의 'Exclusion' 항목이 이 값을 표시.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -21592,22 +21592,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>채광</t>
+          <t>배치(레이아웃)</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Station (crosscut station)</t>
+          <t>Access screen</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>스테이션</t>
+          <t>선별</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>드리프트 상 크로스컷 분기 위치.</t>
+          <t>단계 2·3에서 후보 순서를 정하는 기하 접근 선별(geometric access screen). 후보를 제거하지 않는 순서용 판정.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -21615,22 +21615,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>채광</t>
+          <t>배치(레이아웃)</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Pillar</t>
+          <t>Expanded states (search)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>광주(필러)</t>
+          <t>확장 상태</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>鑛柱. 잔류 암반·광석 기둥.</t>
+          <t>Hybrid-A* 탐색에서 펼친(확장한) 상태 수. 작업 진행률 패널에 표시.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -21638,22 +21638,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>채광</t>
+          <t>배치(레이아웃)</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Rib pillar</t>
+          <t>Layout family</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>리브 필러</t>
+          <t>배치 유형</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>패널 사이 잔류 측벽 광주.</t>
+          <t>램프 배치안의 기하 유형(SPIRAL · LONGITUDINAL · SWITCHBACK).</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -21666,17 +21666,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Minimum pillar</t>
+          <t>Mining method</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>최소 광주 폭</t>
+          <t>채광법</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>인접 스토프 사이 최소 간격.</t>
+          <t>採鑛法.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -21689,17 +21689,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Stope length</t>
+          <t>Longhole open stoping</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>스토프 길이</t>
+          <t>장공 개방 채광법(LHOS)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>주향 방향 채광 단위 길이.</t>
+          <t>HRM: 'Blasthole Stoping and Longhole Open Stoping are frequently used to refer to the same mining method'. 짧은 대안 '장공 채광법'. 국문 표준명은 문헌 추가 확인 필요. · 채광법 이름은 영어명이 현장·문헌에서 더 통용 → 국문명(영어) 병기. 영어명이 길면 업계 약어(LHOS, SLC)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -21712,17 +21712,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Panel</t>
+          <t>Cut and fill</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>패널</t>
+          <t>충전 채광법(Cut &amp; Fill)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>컷앤필 주향 구획.</t>
+          <t>채광법 이름은 영어명이 현장·문헌에서 더 통용 → 국문명(영어) 병기. 영어명이 길면 업계 약어(LHOS, SLC). '컷앤필' 음역 대신 원어</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -21735,17 +21735,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Room and pillar</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>블록</t>
+          <t>주방식 채광법(Room &amp; Pillar)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>컷앤필 레벨 간 채광 구획.</t>
+          <t>채광법 이름은 영어명이 현장·문헌에서 더 통용 → 국문명(영어) 병기. 영어명이 길면 업계 약어(LHOS, SLC)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -21758,17 +21758,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Lift</t>
+          <t>Sublevel caving</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>리프트</t>
+          <t>중단 붕락법(SLC)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>컷앤필 수직 분할층.</t>
+          <t>채광법 이름은 영어명이 현장·문헌에서 더 통용 → 국문명(영어) 병기. 영어명이 길면 업계 약어(LHOS, SLC)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -21781,17 +21781,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Cut</t>
+          <t>Shrinkage stoping</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>컷</t>
+          <t>슈링키지 채광법</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>리프트 내 주향 분할 채굴 단위.</t>
+          <t>미구현(예약). 검토(2026-10): 국문 한자명은 이번 검토에서 문헌 확인을 못 해 음역 유지. · 이미 음역이라 영어 병기 생략</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -21804,17 +21804,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Backfill</t>
+          <t>Stope</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>충전</t>
+          <t>채굴장(스토프)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>充塡. 채굴 공동 되메움.</t>
+          <t>SNU OCW 'Stope: 대형 채굴장', 광산안전기술기준 제44조 '채굴장은 적절한 계단 및 안전한 경사를 유지할 것'. 채굴 후 공동은 같은 조항의 '채굴적'. '스토프'는 외래어 표기법상 맞는 표기(rope→로프)라 괄호 병기. UI의 '스토프'·'채광장'을 '채굴장'으로 통일하는 수정안 기입.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -21827,17 +21827,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Cemented backfill / sill mat</t>
+          <t>Stope access</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>시멘트 충전 / 실매트</t>
+          <t>채굴장 접근부</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>하부 블록 채광을 위한 고결 충전 바닥.</t>
+          <t>Stope → 채굴장 통일. 크로스컷 종점(채굴장 진입점).</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -21850,17 +21850,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Cure</t>
+          <t>Station (crosscut station)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>양생</t>
+          <t>스테이션</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>충전재 경화 기간.</t>
+          <t>드리프트 상 크로스컷 분기 위치.</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -21873,17 +21873,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Room</t>
+          <t>Pillar</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>룸(채광실)</t>
+          <t>광주(필러)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>주방식의 채굴 공간.</t>
+          <t>鑛柱. 잔류 암반·광석 기둥.</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -21896,17 +21896,17 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Heading / Bench</t>
+          <t>Rib pillar</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>헤딩 / 벤치</t>
+          <t>리브 필러</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>룸 선진 굴착 / 하부 벤치 채굴.</t>
+          <t>패널 사이 잔류 측벽 광주.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -21919,17 +21919,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Stoping</t>
+          <t>Minimum pillar</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>채광</t>
+          <t>최소 광주 폭</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>채광 작업 단계(STOPING).</t>
+          <t>인접 스토프 사이 최소 간격.</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -21942,17 +21942,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Mucking</t>
+          <t>Stope length</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>적재(머킹)</t>
+          <t>채굴장 길이</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>파쇄 광석 적재·반출.</t>
+          <t>Stope → 채굴장 통일. UI #118·#119.</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -21965,17 +21965,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Preparation (prep)</t>
+          <t>Panel</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>준비</t>
+          <t>패널</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>채광 준비 작업.</t>
+          <t>컷앤필 주향 구획.</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -21988,17 +21988,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Planned mined tonnes</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>계획 채광량(t)</t>
+          <t>블록</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>굴착 체적×밀도. 자원·매장량이 아님(규칙 198).</t>
+          <t>컷앤필 레벨 간 채광 구획.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -22011,17 +22011,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Grade proxy</t>
+          <t>Lift</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>품위 지표</t>
+          <t>리프트</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>계획용 평균 품위 대용치.</t>
+          <t>컷앤필 수직 분할층.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -22029,22 +22029,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>네트워크·기능</t>
+          <t>채광</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Mine network</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>갱도 네트워크</t>
+          <t>컷</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>노드·간선 그래프.</t>
+          <t>리프트 내 주향 분할 채굴 단위.</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -22052,22 +22052,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>네트워크·기능</t>
+          <t>채광</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Node / Edge</t>
+          <t>Backfill</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>노드 / 간선</t>
+          <t>충전</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>그래프 요소.</t>
+          <t>充塡. 채굴 공동 되메움.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -22075,22 +22075,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>네트워크·기능</t>
+          <t>채광</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Capability</t>
+          <t>Cemented backfill / sill mat</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>시멘트 충전 / 실매트</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>간선이 허용하는 용도(인원·운반·통기·탈출 등). 용량 아님.</t>
+          <t>하부 블록 채광을 위한 고결 충전 바닥.</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -22098,22 +22098,22 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>네트워크·기능</t>
+          <t>채광</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Personnel</t>
+          <t>Cure</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>인원 통행</t>
+          <t>양생</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>인원 이동 가능.</t>
+          <t>충전재 경화 기간.</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -22121,22 +22121,22 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>네트워크·기능</t>
+          <t>채광</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Haulage</t>
+          <t>Room</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>운반</t>
+          <t>룸(채광실)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>광석·폐석 운반.</t>
+          <t>주방식의 채굴 공간.</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -22144,22 +22144,22 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>네트워크·기능</t>
+          <t>채광</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Emergency egress</t>
+          <t>Heading / Bench</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>비상 탈출로</t>
+          <t>헤딩 / 벤치</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>2경로 권고(법적 판정 아님).</t>
+          <t>룸 선진 굴착 / 하부 벤치 채굴.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -22167,22 +22167,22 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>네트워크·기능</t>
+          <t>채광</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Surface-path redundancy</t>
+          <t>Stoping</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>지표 경로 이중화</t>
+          <t>채광</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>간선 분리 경로 수(권고).</t>
+          <t>채광 작업 단계(STOPING).</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -22190,22 +22190,22 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>일정</t>
+          <t>채광</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Schedule / timeline</t>
+          <t>Mucking</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>공정(개발 일정)</t>
+          <t>적재(머킹)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>선후관계 기반 기준 일정. 생산 예측 아님.</t>
+          <t>파쇄 광석 적재·반출.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -22213,22 +22213,22 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>일정</t>
+          <t>채광</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Preparation (prep)</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>작업</t>
+          <t>준비</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>일정 단위.</t>
+          <t>채광 준비 작업.</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -22236,22 +22236,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>일정</t>
+          <t>채광</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Mine life (duration)</t>
+          <t>Planned mined tonnes</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>광산 수명</t>
+          <t>계획 채광량(t)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>년(일) 표기.</t>
+          <t>굴착 체적×밀도. 자원·매장량이 아님(규칙 198).</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -22259,22 +22259,22 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>일정</t>
+          <t>채광</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>First production</t>
+          <t>Grade proxy</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>최초 생산</t>
+          <t>품위 지표</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>첫 STOPING 시작일.</t>
+          <t>계획용 평균 품위 대용치.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -22282,22 +22282,22 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>일정</t>
+          <t>네트워크·기능</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Ramp complete</t>
+          <t>Mine network</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>램프 완료</t>
+          <t>갱도 네트워크</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>램프 굴진 완료일.</t>
+          <t>노드·간선 그래프.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -22305,22 +22305,22 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>일정</t>
+          <t>네트워크·기능</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Development rate</t>
+          <t>Node / Edge</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>굴진 속도</t>
+          <t>노드 / 간선</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>m/일.</t>
+          <t>그래프 요소.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -22328,22 +22328,22 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>네트워크·기능</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Capability</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>통신</t>
+          <t>용도</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>메시 라우터 배치.</t>
+          <t>정의 자체가 '간선이 허용하는 용도(인원·운반·통기·탈출 등). 용량 아님'. '기능'은 장비·시스템의 function으로 읽혀 의미가 흐려짐. 기능 그래프 → 용도 그래프 등 UI 12건 수정안 기입. · 병기는 설명 문장(#271·#824)에만. 카드 제목·단계 칩(#132·#656)은 폭 때문에 '용도' 단독</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -22351,22 +22351,22 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>네트워크·기능</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Mesh router</t>
+          <t>Personnel</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>메시 라우터</t>
+          <t>인원 통행</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>무선 중계기.</t>
+          <t>인원 이동 가능.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -22374,22 +22374,22 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>네트워크·기능</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Haulage</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>통달 범위</t>
+          <t>운반</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>네트워크 측지 거리 기준 커버리지.</t>
+          <t>광석·폐석 운반.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -22397,22 +22397,22 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>네트워크·기능</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Gas sensor</t>
+          <t>Emergency egress</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>가스 센서</t>
+          <t>비상 탈출로</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>가스 감지기.</t>
+          <t>2경로 권고(법적 판정 아님).</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -22420,22 +22420,22 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>네트워크·기능</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Monitoring coverage</t>
+          <t>Surface-path redundancy</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>감시 범위</t>
+          <t>지표 경로 이중화</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>센서 커버리지.</t>
+          <t>간선 분리 경로 수(권고).</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -22443,22 +22443,22 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>일정</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>Schedule / timeline</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>공정(개발 일정)</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>읽기 전용 프로젝션.</t>
+          <t>선후관계 기반 기준 일정. 생산 예측 아님.</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -22466,22 +22466,22 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>일정</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Planning economics</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>계획 경제성</t>
+          <t>작업</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>합성 계획 경제성. 타당성 조사 아님.</t>
+          <t>일정 단위.</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
@@ -22489,22 +22489,22 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>일정</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Mine life (duration)</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>현금흐름</t>
+          <t>광산 수명</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>버킷별.</t>
+          <t>년(일) 표기. 검토(2026-10): 광업 경제성 문헌의 '가행 연한'도 가능. 단 UI 'Baseline duration → 기준 수명'(#380·#491)은 공정의 총 기간이므로 '기준 공정 기간'으로 수정안 기입.</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -22512,22 +22512,22 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>일정</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Planning NPV</t>
+          <t>First production</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>계획 순현재가치(NPV)</t>
+          <t>최초 생산</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>기준 계획 NPV.</t>
+          <t>첫 STOPING 시작일.</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -22535,41 +22535,45 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>일정</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Planning IRR</t>
+          <t>Ramp complete</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>계획 내부수익률(IRR)</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr"/>
+          <t>램프 완료</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>램프 굴진 완료일.</t>
+        </is>
+      </c>
       <c r="E101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>일정</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Discount rate</t>
+          <t>Development rate</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>할인율</t>
+          <t>굴진 속도</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>연 할인율.</t>
+          <t>m/일.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
@@ -22577,22 +22581,22 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Sensitivity</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>민감도</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>±10/20/30 % 격자.</t>
+          <t>메시 라우터 배치.</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -22600,22 +22604,22 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>What-if</t>
+          <t>Mesh router</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>가정 변경</t>
+          <t>메시 라우터</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>WHAT-IF OVERRIDE.</t>
+          <t>무선 중계기.</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
@@ -22623,22 +22627,22 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Design rulebook / assessment</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>설계 규칙 / 설계 평가</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>권위별 체크 표시.</t>
+          <t>'통달(거리)'은 무선 통신 용어로 맞음. 일반 사용자 기준으로는 '통신 범위'도 가능(선택). · '통달'은 무전 전문어라 일반 사용자에게 낯섦. 통신 분야에서 '커버리지'가 통용되고 #427 '레벨 커버리지'와도 통일. 센서 쪽 'Monitoring coverage'는 '감시 범위' 유지</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -22646,22 +22650,22 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Gas sensor</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>권고</t>
+          <t>가스 센서</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>법적·규제 판정 아님.</t>
+          <t>가스 감지기.</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -22669,22 +22673,22 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>내보내기</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Monitoring coverage</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>내보내기</t>
+          <t>감시 범위</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>MineExchange 번들 및 어댑터 패키지.</t>
+          <t>센서 커버리지.</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
@@ -22692,22 +22696,22 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>내보내기</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Import results</t>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>결과 가져오기</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>외부 시뮬레이션 결과(MineResult).</t>
+          <t>읽기 전용 프로젝션.</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -22715,22 +22719,22 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>내보내기</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Simulation results</t>
+          <t>Planning economics</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>시뮬레이션 결과</t>
+          <t>계획 경제성</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Ventsim·AnyLogic 결과 오버레이.</t>
+          <t>합성 계획 경제성. 타당성 조사 아님.</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -22738,22 +22742,22 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>뷰</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Walkthrough</t>
+          <t>Cashflow</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>워크스루</t>
+          <t>현금흐름</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1·3인칭 갱내 탐사 뷰.</t>
+          <t>버킷별.</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -22761,41 +22765,45 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>뷰</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Minimap</t>
+          <t>Planning NPV</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>미니맵</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr"/>
+          <t>계획 순현재가치(NPV)</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>기준 계획 NPV.</t>
+        </is>
+      </c>
       <c r="E111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>뷰</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Go to</t>
+          <t>Planning IRR</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>이동</t>
+          <t>계획 내부수익률(IRR)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>램프 분기부로 순간 이동.</t>
+          <t>계획 현금흐름의 내부수익률. 순현금흐름 부호가 한 번만 바뀔 때만 정의되며, 아니면 미정의 사유를 표시.</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -22803,22 +22811,22 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>뷰</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Discount rate</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>레이어</t>
+          <t>할인율</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>표시 레이어.</t>
+          <t>연 할인율.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -22826,22 +22834,22 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>셸</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Setup / Design / Network / Mining / Systems / Analysis / Export</t>
+          <t>Sensitivity</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>설정 / 설계 / 네트워크 / 채광 / 시스템 / 분석 / 내보내기</t>
+          <t>민감도</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>리본 7단계.</t>
+          <t>±10/20/30 % 격자.</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -22849,22 +22857,22 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>셸</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Reset mine</t>
+          <t>What-if</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>광산 초기화</t>
+          <t>What-if</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>생성된 월드로 되돌림.</t>
+          <t>'What-if 분석'이 국내 업무 용어로 통용(#408)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -22872,22 +22880,22 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>셸</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Reset from &lt;stage&gt;</t>
+          <t>Design rulebook / assessment</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>&lt;단계&gt;부터 초기화</t>
+          <t>설계 규칙 / 설계 평가</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>해당 단계 이후 산출물 삭제.</t>
+          <t>권위별 체크 표시.</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -22895,41 +22903,45 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>셸</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Generate / Regenerate</t>
+          <t>Advisory</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>생성 / 재생성</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr"/>
+          <t>권고</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>법적·규제 판정 아님.</t>
+        </is>
+      </c>
       <c r="E117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>셸</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Ready / Running / Failed / Not generated</t>
+          <t>Authority (assessment)</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>준비됨 / 실행 중 / 실패 / 미생성</t>
+          <t>판정 유형</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>상태 배지.</t>
+          <t>설계 평가 항목의 판정 종류: HARD_DESIGN_RULE · DERIVED_VALIDATION · ADVISORY · INFORMATIONAL. 배치 순위의 'layout authority'는 '배치 결과 기준'.</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -22937,22 +22949,22 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>내보내기</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Articulated dump truck (ADT)</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>굴절식 덤프트럭(ADT)</t>
+          <t>내보내기</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>갱내 운반에 쓰이는 굴절식(앞·뒤 차체가 힌지로 연결된) 덤프트럭. 현장에서는 'ADT'를 그대로 부르는 경우가 많아 괄호로 병기. 워크스루 차량 프리셋은 대표 등급 제원(45 t·60 t급)이며 제조사 사양이 아님.</t>
+          <t>MineExchange 번들 및 어댑터 패키지.</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -22960,22 +22972,22 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>내보내기</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Rigid dump truck (RDT)</t>
+          <t>Import results</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>리지드 덤프트럭(RDT)</t>
+          <t>결과 가져오기</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>일체형(비굴절) 차체의 덤프트럭. 주로 노천용 대형 차체로, 워크스루에서는 비교용 40 t급 프리셋으로만 제공.</t>
+          <t>외부 시뮬레이션 결과(MineResult).</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -22983,22 +22995,22 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>워크스루</t>
+          <t>내보내기</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Chase camera</t>
+          <t>Simulation results</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>추적 카메라</t>
+          <t>시뮬레이션 결과</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>3인칭 시점에서 아바타(사람·차량·드론)를 뒤에서 따라가는 카메라. 게임 용어 '추적(체이스) 카메라'를 채택.</t>
+          <t>Ventsim·AnyLogic 결과 오버레이.</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -23006,25 +23018,301 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>뷰</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Walkthrough</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
           <t>워크스루</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>1·3인칭 갱내 탐사 뷰.</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>뷰</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Minimap</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>미니맵</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>워크스루 화면 구석의 평면 위치도(현재 위치·방향).</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>뷰</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Go to</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>램프 분기부로 순간 이동.</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>뷰</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>레이어</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>표시 레이어.</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>셸</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Setup / Design / Network / Mining / Systems / Analysis / Export</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>설정 / 설계 / 네트워크 / 채광 / 시스템 / 분석 / 내보내기</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>리본 7단계.</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>셸</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Reset mine</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>광산 초기화</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>생성된 월드로 되돌림.</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>셸</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Reset from &lt;stage&gt;</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>&lt;단계&gt;부터 초기화</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>해당 단계 이후 산출물 삭제.</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>셸</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Generate / Regenerate</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>생성 / 재생성</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>백엔드 산출물 생성 / 기존 산출물을 지우고 다시 생성.</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>셸</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Ready / Running / Failed / Not generated</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>준비됨 / 실행 중 / 실패 / 미생성</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>상태 배지.</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Articulated dump truck (ADT)</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>굴절식 덤프트럭(ADT)</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>갱내 운반에 쓰이는 굴절식(앞·뒤 차체가 힌지로 연결된) 덤프트럭. 현장에서는 'ADT'를 그대로 부르는 경우가 많아 괄호로 병기. 워크스루 차량 프리셋은 대표 등급 제원(45 t·60 t급)이며 제조사 사양이 아님.</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Rigid dump truck (RDT)</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>리지드 덤프트럭(RDT)</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>일체형(비굴절) 차체의 덤프트럭. 주로 노천용 대형 차체로, 워크스루에서는 비교용 40 t급 프리셋으로만 제공.</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>워크스루</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Chase camera</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>추적 카메라</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>3인칭 시점에서 아바타(사람·차량·드론)를 뒤에서 따라가는 카메라. 게임 용어 '추적(체이스) 카메라'를 채택.</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>워크스루</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Level ladder</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>레벨 사다리</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>미니맵 옆의 세로 표고 축: 각 레벨 눈금과 현재 RL 위치. 광산의 '레벨 단면도'와 구분되는 UI 보조 요소라 직역을 채택.</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
